--- a/Test_data/Boolean and force tests/Master charts.xlsx
+++ b/Test_data/Boolean and force tests/Master charts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dokumenter\Skole\Master\Master-s-Thesis\Test_data\Boolean and force tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6229FFDC-7FD3-42D8-BBA2-D6D773C78817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9594BC-FAE4-4C95-BE36-C5E14FECA0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="9" xr2:uid="{183E3E47-5F56-400D-983A-CDA78A52BF4C}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" firstSheet="1" activeTab="1" xr2:uid="{183E3E47-5F56-400D-983A-CDA78A52BF4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" state="hidden" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="128">
   <si>
     <t>Time</t>
   </si>
@@ -62,12 +62,6 @@
     <t>Ordinary basil</t>
   </si>
   <si>
-    <t>Malachai Cale</t>
-  </si>
-  <si>
-    <t>Green Salad</t>
-  </si>
-  <si>
     <t>Fail = 0</t>
   </si>
   <si>
@@ -140,9 +134,6 @@
     <t>Seed Type</t>
   </si>
   <si>
-    <t>S</t>
-  </si>
-  <si>
     <t>B</t>
   </si>
   <si>
@@ -212,9 +203,6 @@
     <t>New Plug</t>
   </si>
   <si>
-    <t>Success rate</t>
-  </si>
-  <si>
     <t>Used Plug</t>
   </si>
   <si>
@@ -230,12 +218,6 @@
     <t xml:space="preserve">Aerated </t>
   </si>
   <si>
-    <t>Malachai Kale</t>
-  </si>
-  <si>
-    <t>Plug Growth</t>
-  </si>
-  <si>
     <t>Runs</t>
   </si>
   <si>
@@ -423,6 +405,30 @@
   </si>
   <si>
     <t>Unit costs</t>
+  </si>
+  <si>
+    <t>Success(0/1)</t>
+  </si>
+  <si>
+    <t>Plug Growth[weeks]</t>
+  </si>
+  <si>
+    <t>Kale</t>
+  </si>
+  <si>
+    <t>Success [%]</t>
+  </si>
+  <si>
+    <t>Green lettuce</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>L= Lettuce</t>
+  </si>
+  <si>
+    <t>B= Basil</t>
   </si>
 </sst>
 </file>
@@ -433,7 +439,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -467,13 +473,58 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -489,6 +540,21 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -544,12 +610,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -565,14 +634,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -589,10 +654,18 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="5" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="8" fillId="5" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="6">
+    <cellStyle name="Dårlig" xfId="4" builtinId="27"/>
+    <cellStyle name="God" xfId="3" builtinId="26"/>
     <cellStyle name="Hyperkobling" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Nøytral" xfId="5" builtinId="28"/>
     <cellStyle name="Utdata" xfId="1" builtinId="21"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2449,36 +2522,36 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B3">
         <v>270</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -2488,21 +2561,21 @@
         <v>270</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B4">
         <v>176</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -2512,21 +2585,21 @@
         <v>176</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B5">
         <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -2536,21 +2609,21 @@
         <v>97</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B6">
         <v>452</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -2560,21 +2633,21 @@
         <v>904</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B7">
         <v>394</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -2584,21 +2657,21 @@
         <v>394</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B8">
         <v>250</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -2608,21 +2681,21 @@
         <v>250</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B9">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -2632,21 +2705,21 @@
         <v>150</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B10">
         <v>106</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -2656,21 +2729,21 @@
         <v>106</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B11">
         <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -2680,21 +2753,21 @@
         <v>71</v>
       </c>
       <c r="F11" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B12">
         <v>231</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -2704,21 +2777,21 @@
         <v>462</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B13">
         <v>149</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2728,21 +2801,21 @@
         <v>149</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B14">
         <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2752,21 +2825,21 @@
         <v>60</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B15">
         <v>290</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2776,21 +2849,21 @@
         <v>290</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B16">
         <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -2800,21 +2873,21 @@
         <v>152</v>
       </c>
       <c r="F16" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B17">
         <v>369</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2824,29 +2897,29 @@
         <v>369</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E18">
         <v>226</v>
       </c>
       <c r="F18" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -2856,41 +2929,41 @@
         <v>4126</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B26">
         <v>270</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -2900,21 +2973,21 @@
         <v>270</v>
       </c>
       <c r="F26" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B27">
         <v>176</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -2924,21 +2997,21 @@
         <v>176</v>
       </c>
       <c r="F27" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B28">
         <v>394</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -2948,21 +3021,21 @@
         <v>394</v>
       </c>
       <c r="F28" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B29">
         <v>250</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -2972,21 +3045,21 @@
         <v>250</v>
       </c>
       <c r="F29" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B30">
         <v>106</v>
       </c>
       <c r="C30" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -2996,21 +3069,21 @@
         <v>106</v>
       </c>
       <c r="F30" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B31">
         <v>231</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -3020,21 +3093,21 @@
         <v>462</v>
       </c>
       <c r="F31" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B32">
         <v>60</v>
       </c>
       <c r="C32" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -3044,21 +3117,21 @@
         <v>60</v>
       </c>
       <c r="F32" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B33">
         <v>290</v>
       </c>
       <c r="C33" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -3068,21 +3141,21 @@
         <v>290</v>
       </c>
       <c r="F33" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B34">
         <v>369</v>
       </c>
       <c r="C34" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -3092,15 +3165,15 @@
         <v>369</v>
       </c>
       <c r="F34" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -3110,7 +3183,7 @@
         <v>2377</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -3158,361 +3231,389 @@
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="19">
+        <v>1</v>
+      </c>
+      <c r="B3" s="19">
+        <v>1</v>
+      </c>
+      <c r="C3" s="19">
+        <v>2</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" s="19">
+        <v>1</v>
+      </c>
+      <c r="F3" s="19">
+        <v>1</v>
+      </c>
+      <c r="G3" s="19">
+        <v>1</v>
+      </c>
+      <c r="H3" s="19">
+        <v>1</v>
+      </c>
+      <c r="I3" s="19"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="19">
+        <v>2</v>
+      </c>
+      <c r="B4" s="19">
+        <v>1</v>
+      </c>
+      <c r="C4" s="19">
+        <v>3</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" s="19">
+        <v>1</v>
+      </c>
+      <c r="F4" s="19">
+        <v>1</v>
+      </c>
+      <c r="G4" s="19">
+        <v>1</v>
+      </c>
+      <c r="H4" s="19">
+        <v>1</v>
+      </c>
+      <c r="I4" s="19"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="19">
+        <v>3</v>
+      </c>
+      <c r="B5" s="19">
+        <v>1</v>
+      </c>
+      <c r="C5" s="19">
+        <v>3</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" s="19">
+        <v>1</v>
+      </c>
+      <c r="F5" s="19">
+        <v>1</v>
+      </c>
+      <c r="G5" s="19">
+        <v>1</v>
+      </c>
+      <c r="H5" s="19">
+        <v>0</v>
+      </c>
+      <c r="I5" s="19"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="19">
+        <v>4</v>
+      </c>
+      <c r="B6" s="19">
+        <v>1</v>
+      </c>
+      <c r="C6" s="19">
+        <v>2</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E6" s="19">
+        <v>1</v>
+      </c>
+      <c r="F6" s="19">
+        <v>1</v>
+      </c>
+      <c r="G6" s="19">
+        <v>1</v>
+      </c>
+      <c r="H6" s="19">
+        <v>1</v>
+      </c>
+      <c r="I6" s="19"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="19">
+        <v>5</v>
+      </c>
+      <c r="B7" s="19">
+        <v>1</v>
+      </c>
+      <c r="C7" s="19">
+        <v>3</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E7" s="19">
+        <v>1</v>
+      </c>
+      <c r="F7" s="19">
+        <v>1</v>
+      </c>
+      <c r="G7" s="19">
+        <v>1</v>
+      </c>
+      <c r="H7" s="19">
+        <v>1</v>
+      </c>
+      <c r="I7" s="19"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="19">
+        <v>6</v>
+      </c>
+      <c r="B8" s="19">
+        <v>1</v>
+      </c>
+      <c r="C8" s="19">
+        <v>2</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" s="19">
+        <v>1</v>
+      </c>
+      <c r="F8" s="19">
+        <v>1</v>
+      </c>
+      <c r="G8" s="19">
+        <v>1</v>
+      </c>
+      <c r="H8" s="19">
+        <v>1</v>
+      </c>
+      <c r="I8" s="19"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="19">
+        <v>7</v>
+      </c>
+      <c r="B9" s="19">
+        <v>1</v>
+      </c>
+      <c r="C9" s="19">
+        <v>4</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="19">
+        <v>1</v>
+      </c>
+      <c r="F9" s="19">
+        <v>1</v>
+      </c>
+      <c r="G9" s="19">
+        <v>1</v>
+      </c>
+      <c r="H9" s="19">
+        <v>0</v>
+      </c>
+      <c r="I9" s="19"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="19">
+        <v>8</v>
+      </c>
+      <c r="B10" s="19">
+        <v>1</v>
+      </c>
+      <c r="C10" s="19">
+        <v>3</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="19">
+        <v>1</v>
+      </c>
+      <c r="F10" s="19">
+        <v>1</v>
+      </c>
+      <c r="G10" s="19">
+        <v>1</v>
+      </c>
+      <c r="H10" s="19">
+        <v>1</v>
+      </c>
+      <c r="I10" s="19"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="19">
         <v>9</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="B11" s="19">
+        <v>1</v>
+      </c>
+      <c r="C11" s="19">
         <v>4</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>5</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>6</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>7</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
+      <c r="D11" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="19">
+        <v>1</v>
+      </c>
+      <c r="F11" s="19">
+        <v>1</v>
+      </c>
+      <c r="G11" s="19">
+        <v>1</v>
+      </c>
+      <c r="H11" s="19">
+        <v>1</v>
+      </c>
+      <c r="I11" s="19"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="19">
+        <v>10</v>
+      </c>
+      <c r="B12" s="19">
+        <v>1</v>
+      </c>
+      <c r="C12" s="19">
         <v>4</v>
       </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>8</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>9</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="D12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
+      <c r="D12" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="19">
+        <v>1</v>
+      </c>
+      <c r="F12" s="19">
+        <v>1</v>
+      </c>
+      <c r="G12" s="19">
+        <v>1</v>
+      </c>
+      <c r="H12" s="19">
+        <v>0</v>
+      </c>
+      <c r="I12" s="19"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>10</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>4</v>
-      </c>
-      <c r="D13" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14">
-        <f>SUM(B4:B13)/COUNTA(B4:B13)*100</f>
+      <c r="A13" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" s="32">
+        <f>SUM(B3:B12)/COUNTA(B3:B12)*100</f>
         <v>100</v>
       </c>
-      <c r="E14">
-        <f t="shared" ref="E14" si="0">SUM(E4:E13)/COUNTA(E4:E13)*100</f>
+      <c r="C13" s="30"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="32">
+        <f t="shared" ref="E13" si="0">SUM(E3:E12)/COUNTA(E3:E12)*100</f>
         <v>100</v>
       </c>
-      <c r="F14">
-        <f t="shared" ref="F14" si="1">SUM(F4:F13)/COUNTA(F4:F13)*100</f>
+      <c r="F13" s="32">
+        <f t="shared" ref="F13" si="1">SUM(F3:F12)/COUNTA(F3:F12)*100</f>
         <v>100</v>
       </c>
-      <c r="G14">
-        <f t="shared" ref="G14" si="2">SUM(G4:G13)/COUNTA(G4:G13)*100</f>
+      <c r="G13" s="32">
+        <f t="shared" ref="G13" si="2">SUM(G3:G12)/COUNTA(G3:G12)*100</f>
         <v>100</v>
       </c>
-      <c r="H14">
-        <f t="shared" ref="H14" si="3">SUM(H4:H13)/COUNTA(H4:H13)*100</f>
+      <c r="H13" s="30">
+        <f t="shared" ref="H13" si="3">SUM(H3:H12)/COUNTA(H3:H12)*100</f>
         <v>70</v>
       </c>
-      <c r="I14" s="1">
-        <f>(B14*E14*F14*G14*H14)/100^4</f>
+      <c r="I13" s="30">
+        <f>(B13*E13*F13*G13*H13)/100^4</f>
         <v>70</v>
       </c>
     </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" s="29">
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+    </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>114</v>
-      </c>
-      <c r="B17" s="3">
-        <v>0.46666666666666667</v>
-      </c>
+      <c r="A17" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="30">
+        <f>I13/100</f>
+        <v>0.7</v>
+      </c>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>115</v>
-      </c>
-      <c r="B18">
-        <f>I14/100</f>
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B19" s="3">
-        <f>B17*B18</f>
+      <c r="A18" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" s="29">
+        <f>B16*B17</f>
         <v>0.32666666666666666</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D19" s="14">
-        <f>B19*100</f>
+      <c r="C18" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" s="31">
+        <f>B18*100</f>
         <v>32.666666666666664</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>53</v>
+      <c r="E18" s="18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="33" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="33" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="50" spans="4:4" x14ac:dyDescent="0.3">
@@ -3529,13 +3630,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55E288FA-CE0E-414A-B0A2-7E8AE2BDA4EE}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.88671875" style="8" customWidth="1"/>
-    <col min="2" max="2" width="12" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="11.5546875" style="8"/>
+    <col min="2" max="2" width="13" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="8"/>
+    <col min="6" max="6" width="12.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.5546875" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -3543,964 +3647,964 @@
         <v>2</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="14">
+        <v>1</v>
+      </c>
+      <c r="B4" s="14">
+        <v>1</v>
+      </c>
+      <c r="C4" s="14">
+        <v>3</v>
+      </c>
+      <c r="D4" s="14">
+        <v>1</v>
+      </c>
+      <c r="E4" s="14">
+        <v>3</v>
+      </c>
+      <c r="F4" s="14">
+        <v>1</v>
+      </c>
+      <c r="G4" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="14">
+        <v>2</v>
+      </c>
+      <c r="B5" s="14">
+        <v>1</v>
+      </c>
+      <c r="C5" s="14">
+        <v>3</v>
+      </c>
+      <c r="D5" s="14">
+        <v>1</v>
+      </c>
+      <c r="E5" s="14">
+        <v>1</v>
+      </c>
+      <c r="F5" s="14">
+        <v>1</v>
+      </c>
+      <c r="G5" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="14">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14">
+        <v>1</v>
+      </c>
+      <c r="C6" s="14">
+        <v>3</v>
+      </c>
+      <c r="D6" s="14">
+        <v>1</v>
+      </c>
+      <c r="E6" s="14">
+        <v>1</v>
+      </c>
+      <c r="F6" s="14">
+        <v>1</v>
+      </c>
+      <c r="G6" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="14">
+        <v>4</v>
+      </c>
+      <c r="B7" s="14">
+        <v>1</v>
+      </c>
+      <c r="C7" s="14">
+        <v>3</v>
+      </c>
+      <c r="D7" s="14">
+        <v>1</v>
+      </c>
+      <c r="E7" s="14">
+        <v>1</v>
+      </c>
+      <c r="F7" s="14">
+        <v>1</v>
+      </c>
+      <c r="G7" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="14">
+        <v>5</v>
+      </c>
+      <c r="B8" s="14">
+        <v>1</v>
+      </c>
+      <c r="C8" s="14">
+        <v>3</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
+      <c r="F8" s="14">
+        <v>1</v>
+      </c>
+      <c r="G8" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="14">
+        <v>6</v>
+      </c>
+      <c r="B9" s="14">
+        <v>1</v>
+      </c>
+      <c r="C9" s="14">
+        <v>3</v>
+      </c>
+      <c r="D9" s="14">
+        <v>1</v>
+      </c>
+      <c r="E9" s="14">
+        <v>1</v>
+      </c>
+      <c r="F9" s="14">
+        <v>1</v>
+      </c>
+      <c r="G9" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="14">
+        <v>7</v>
+      </c>
+      <c r="B10" s="14">
+        <v>1</v>
+      </c>
+      <c r="C10" s="14">
+        <v>4</v>
+      </c>
+      <c r="D10" s="14">
+        <v>1</v>
+      </c>
+      <c r="E10" s="14">
+        <v>1</v>
+      </c>
+      <c r="F10" s="14">
+        <v>1</v>
+      </c>
+      <c r="G10" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="14">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+      <c r="B11" s="14">
+        <v>1</v>
+      </c>
+      <c r="C11" s="14">
+        <v>2</v>
+      </c>
+      <c r="D11" s="14">
+        <v>1</v>
+      </c>
+      <c r="E11" s="14">
+        <v>1</v>
+      </c>
+      <c r="F11" s="14">
+        <v>1</v>
+      </c>
+      <c r="G11" s="14">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="s">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="14">
+        <v>9</v>
+      </c>
+      <c r="B12" s="14">
+        <v>1</v>
+      </c>
+      <c r="C12" s="14">
+        <v>2</v>
+      </c>
+      <c r="D12" s="14">
+        <v>1</v>
+      </c>
+      <c r="E12" s="14">
+        <v>1</v>
+      </c>
+      <c r="F12" s="14">
+        <v>1</v>
+      </c>
+      <c r="G12" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="14">
+        <v>10</v>
+      </c>
+      <c r="B13" s="14">
+        <v>1</v>
+      </c>
+      <c r="C13" s="14">
+        <v>3</v>
+      </c>
+      <c r="D13" s="14">
+        <v>1</v>
+      </c>
+      <c r="E13" s="14">
+        <v>1</v>
+      </c>
+      <c r="F13" s="14">
+        <v>1</v>
+      </c>
+      <c r="G13" s="14">
         <v>4</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="14">
+        <v>11</v>
+      </c>
+      <c r="B14" s="14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="14">
+        <v>3</v>
+      </c>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="14">
+        <v>1</v>
+      </c>
+      <c r="F14" s="14">
+        <v>1</v>
+      </c>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="14">
+        <v>12</v>
+      </c>
+      <c r="B15" s="14">
+        <v>1</v>
+      </c>
+      <c r="C15" s="14">
+        <v>3</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>1</v>
+      </c>
+      <c r="F15" s="14">
+        <v>1</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="14">
+        <v>13</v>
+      </c>
+      <c r="B16" s="14">
+        <v>1</v>
+      </c>
+      <c r="C16" s="14">
+        <v>3</v>
+      </c>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="14">
+        <v>1</v>
+      </c>
+      <c r="F16" s="14">
+        <v>1</v>
+      </c>
+      <c r="G16" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="14">
+        <v>14</v>
+      </c>
+      <c r="B17" s="14">
+        <v>1</v>
+      </c>
+      <c r="C17" s="14">
+        <v>2</v>
+      </c>
+      <c r="D17" s="14">
+        <v>1</v>
+      </c>
+      <c r="E17" s="14">
+        <v>1</v>
+      </c>
+      <c r="F17" s="14">
+        <v>1</v>
+      </c>
+      <c r="G17" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="14">
+        <v>15</v>
+      </c>
+      <c r="B18" s="14">
+        <v>1</v>
+      </c>
+      <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="14">
+        <v>1</v>
+      </c>
+      <c r="F18" s="14">
+        <v>1</v>
+      </c>
+      <c r="G18" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="14">
+        <v>16</v>
+      </c>
+      <c r="B19" s="14">
+        <v>1</v>
+      </c>
+      <c r="C19" s="14">
+        <v>3</v>
+      </c>
+      <c r="D19" s="14">
+        <v>1</v>
+      </c>
+      <c r="E19" s="14">
+        <v>1</v>
+      </c>
+      <c r="F19" s="14">
+        <v>1</v>
+      </c>
+      <c r="G19" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="14">
+        <v>17</v>
+      </c>
+      <c r="B20" s="14">
+        <v>1</v>
+      </c>
+      <c r="C20" s="14">
+        <v>3</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14">
+        <v>1</v>
+      </c>
+      <c r="F20" s="14">
+        <v>1</v>
+      </c>
+      <c r="G20" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="14">
+        <v>18</v>
+      </c>
+      <c r="B21" s="14">
+        <v>1</v>
+      </c>
+      <c r="C21" s="14">
+        <v>2</v>
+      </c>
+      <c r="D21" s="14">
+        <v>1</v>
+      </c>
+      <c r="E21" s="14">
+        <v>1</v>
+      </c>
+      <c r="F21" s="14">
+        <v>1</v>
+      </c>
+      <c r="G21" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="14">
+        <v>19</v>
+      </c>
+      <c r="B22" s="14">
+        <v>1</v>
+      </c>
+      <c r="C22" s="14">
+        <v>3</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>1</v>
+      </c>
+      <c r="F22" s="14">
+        <v>1</v>
+      </c>
+      <c r="G22" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="15">
+        <v>20</v>
+      </c>
+      <c r="B23" s="15">
+        <v>1</v>
+      </c>
+      <c r="C23" s="15">
+        <v>3</v>
+      </c>
+      <c r="D23" s="15">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>1</v>
+      </c>
+      <c r="F23" s="15">
+        <v>1</v>
+      </c>
+      <c r="G23" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="16">
-        <v>1</v>
-      </c>
-      <c r="B6" s="16">
-        <v>1</v>
-      </c>
-      <c r="C6" s="16">
-        <v>3</v>
-      </c>
-      <c r="D6" s="16">
-        <v>1</v>
-      </c>
-      <c r="E6" s="16">
-        <v>3</v>
-      </c>
-      <c r="F6" s="16">
-        <v>1</v>
-      </c>
-      <c r="G6" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="16">
-        <v>2</v>
-      </c>
-      <c r="B7" s="16">
-        <v>1</v>
-      </c>
-      <c r="C7" s="16">
-        <v>3</v>
-      </c>
-      <c r="D7" s="16">
-        <v>1</v>
-      </c>
-      <c r="E7" s="16">
-        <v>1</v>
-      </c>
-      <c r="F7" s="16">
-        <v>1</v>
-      </c>
-      <c r="G7" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="16">
-        <v>3</v>
-      </c>
-      <c r="B8" s="16">
-        <v>1</v>
-      </c>
-      <c r="C8" s="16">
-        <v>3</v>
-      </c>
-      <c r="D8" s="16">
-        <v>1</v>
-      </c>
-      <c r="E8" s="16">
-        <v>1</v>
-      </c>
-      <c r="F8" s="16">
-        <v>1</v>
-      </c>
-      <c r="G8" s="16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="16">
-        <v>4</v>
-      </c>
-      <c r="B9" s="16">
-        <v>1</v>
-      </c>
-      <c r="C9" s="16">
-        <v>3</v>
-      </c>
-      <c r="D9" s="16">
-        <v>1</v>
-      </c>
-      <c r="E9" s="16">
-        <v>1</v>
-      </c>
-      <c r="F9" s="16">
-        <v>1</v>
-      </c>
-      <c r="G9" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="16">
-        <v>5</v>
-      </c>
-      <c r="B10" s="16">
-        <v>1</v>
-      </c>
-      <c r="C10" s="16">
-        <v>3</v>
-      </c>
-      <c r="D10" s="16">
-        <v>1</v>
-      </c>
-      <c r="E10" s="16">
-        <v>1</v>
-      </c>
-      <c r="F10" s="16">
-        <v>1</v>
-      </c>
-      <c r="G10" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="16">
-        <v>6</v>
-      </c>
-      <c r="B11" s="16">
-        <v>1</v>
-      </c>
-      <c r="C11" s="16">
-        <v>3</v>
-      </c>
-      <c r="D11" s="16">
-        <v>1</v>
-      </c>
-      <c r="E11" s="16">
-        <v>1</v>
-      </c>
-      <c r="F11" s="16">
-        <v>1</v>
-      </c>
-      <c r="G11" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="16">
-        <v>7</v>
-      </c>
-      <c r="B12" s="16">
-        <v>1</v>
-      </c>
-      <c r="C12" s="16">
-        <v>4</v>
-      </c>
-      <c r="D12" s="16">
-        <v>1</v>
-      </c>
-      <c r="E12" s="16">
-        <v>1</v>
-      </c>
-      <c r="F12" s="16">
-        <v>1</v>
-      </c>
-      <c r="G12" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="16">
-        <v>8</v>
-      </c>
-      <c r="B13" s="16">
-        <v>1</v>
-      </c>
-      <c r="C13" s="16">
-        <v>2</v>
-      </c>
-      <c r="D13" s="16">
-        <v>1</v>
-      </c>
-      <c r="E13" s="16">
-        <v>1</v>
-      </c>
-      <c r="F13" s="16">
-        <v>1</v>
-      </c>
-      <c r="G13" s="16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="16">
-        <v>9</v>
-      </c>
-      <c r="B14" s="16">
-        <v>1</v>
-      </c>
-      <c r="C14" s="16">
-        <v>2</v>
-      </c>
-      <c r="D14" s="16">
-        <v>1</v>
-      </c>
-      <c r="E14" s="16">
-        <v>1</v>
-      </c>
-      <c r="F14" s="16">
-        <v>1</v>
-      </c>
-      <c r="G14" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="16">
-        <v>10</v>
-      </c>
-      <c r="B15" s="16">
-        <v>1</v>
-      </c>
-      <c r="C15" s="16">
-        <v>3</v>
-      </c>
-      <c r="D15" s="16">
-        <v>1</v>
-      </c>
-      <c r="E15" s="16">
-        <v>1</v>
-      </c>
-      <c r="F15" s="16">
-        <v>1</v>
-      </c>
-      <c r="G15" s="16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="16">
-        <v>11</v>
-      </c>
-      <c r="B16" s="16">
-        <v>1</v>
-      </c>
-      <c r="C16" s="16">
-        <v>3</v>
-      </c>
-      <c r="D16" s="16">
-        <v>1</v>
-      </c>
-      <c r="E16" s="16">
-        <v>1</v>
-      </c>
-      <c r="F16" s="16">
-        <v>1</v>
-      </c>
-      <c r="G16" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="16">
-        <v>12</v>
-      </c>
-      <c r="B17" s="16">
-        <v>1</v>
-      </c>
-      <c r="C17" s="16">
-        <v>3</v>
-      </c>
-      <c r="D17" s="16">
-        <v>1</v>
-      </c>
-      <c r="E17" s="16">
-        <v>1</v>
-      </c>
-      <c r="F17" s="16">
-        <v>1</v>
-      </c>
-      <c r="G17" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="16">
-        <v>13</v>
-      </c>
-      <c r="B18" s="16">
-        <v>1</v>
-      </c>
-      <c r="C18" s="16">
-        <v>3</v>
-      </c>
-      <c r="D18" s="16">
-        <v>1</v>
-      </c>
-      <c r="E18" s="16">
-        <v>1</v>
-      </c>
-      <c r="F18" s="16">
-        <v>1</v>
-      </c>
-      <c r="G18" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="16">
-        <v>14</v>
-      </c>
-      <c r="B19" s="16">
-        <v>1</v>
-      </c>
-      <c r="C19" s="16">
-        <v>2</v>
-      </c>
-      <c r="D19" s="16">
-        <v>1</v>
-      </c>
-      <c r="E19" s="16">
-        <v>1</v>
-      </c>
-      <c r="F19" s="16">
-        <v>1</v>
-      </c>
-      <c r="G19" s="16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="16">
-        <v>15</v>
-      </c>
-      <c r="B20" s="16">
-        <v>1</v>
-      </c>
-      <c r="C20" s="16">
-        <v>3</v>
-      </c>
-      <c r="D20" s="16">
-        <v>1</v>
-      </c>
-      <c r="E20" s="16">
-        <v>1</v>
-      </c>
-      <c r="F20" s="16">
-        <v>1</v>
-      </c>
-      <c r="G20" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="16">
-        <v>16</v>
-      </c>
-      <c r="B21" s="16">
-        <v>1</v>
-      </c>
-      <c r="C21" s="16">
-        <v>3</v>
-      </c>
-      <c r="D21" s="16">
-        <v>1</v>
-      </c>
-      <c r="E21" s="16">
-        <v>1</v>
-      </c>
-      <c r="F21" s="16">
-        <v>1</v>
-      </c>
-      <c r="G21" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="16">
-        <v>17</v>
-      </c>
-      <c r="B22" s="16">
-        <v>1</v>
-      </c>
-      <c r="C22" s="16">
-        <v>3</v>
-      </c>
-      <c r="D22" s="16">
-        <v>1</v>
-      </c>
-      <c r="E22" s="16">
-        <v>1</v>
-      </c>
-      <c r="F22" s="16">
-        <v>1</v>
-      </c>
-      <c r="G22" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="16">
-        <v>18</v>
-      </c>
-      <c r="B23" s="16">
-        <v>1</v>
-      </c>
-      <c r="C23" s="16">
-        <v>2</v>
-      </c>
-      <c r="D23" s="16">
-        <v>1</v>
-      </c>
-      <c r="E23" s="16">
-        <v>1</v>
-      </c>
-      <c r="F23" s="16">
-        <v>1</v>
-      </c>
-      <c r="G23" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="16">
-        <v>19</v>
-      </c>
-      <c r="B24" s="16">
-        <v>1</v>
-      </c>
-      <c r="C24" s="16">
-        <v>3</v>
-      </c>
-      <c r="D24" s="16">
-        <v>1</v>
-      </c>
-      <c r="E24" s="16">
-        <v>1</v>
-      </c>
-      <c r="F24" s="16">
-        <v>1</v>
-      </c>
-      <c r="G24" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="17">
-        <v>20</v>
-      </c>
-      <c r="B25" s="17">
-        <v>1</v>
-      </c>
-      <c r="C25" s="17">
-        <v>3</v>
-      </c>
-      <c r="D25" s="17">
-        <v>1</v>
-      </c>
-      <c r="E25" s="17">
-        <v>1</v>
-      </c>
-      <c r="F25" s="17">
-        <v>1</v>
-      </c>
-      <c r="G25" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B26" s="10">
-        <f>SUM(B6:B25)/COUNT(B6:B25)</f>
-        <v>1</v>
-      </c>
-      <c r="C26" s="10">
-        <f t="shared" ref="C26:G26" si="0">SUM(C6:C25)/COUNT(C6:C25)</f>
+      <c r="B24" s="10">
+        <f>SUM(B4:B23)/COUNT(B4:B23)</f>
+        <v>1</v>
+      </c>
+      <c r="C24" s="10">
+        <f t="shared" ref="C24:G24" si="0">SUM(C4:C23)/COUNT(C4:C23)</f>
         <v>2.85</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D24" s="10">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E24" s="10">
         <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F24" s="10">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G24" s="10">
         <f t="shared" si="0"/>
         <v>1.75</v>
       </c>
     </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="10">
+        <f>_xlfn.STDEV.S(B4:B23)</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="13">
+        <f t="shared" ref="C25:G25" si="1">_xlfn.STDEV.S(C4:C23)</f>
+        <v>0.4893604849295935</v>
+      </c>
+      <c r="D25" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E25" s="13">
+        <f t="shared" si="1"/>
+        <v>0.44721359549995798</v>
+      </c>
+      <c r="F25" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="13">
+        <f t="shared" si="1"/>
+        <v>0.91046546800032602</v>
+      </c>
+    </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="16">
+        <v>1</v>
+      </c>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17">
+        <v>1</v>
+      </c>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17">
+        <v>1</v>
+      </c>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="16">
+        <v>2</v>
+      </c>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17">
+        <v>1</v>
+      </c>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17">
+        <v>1</v>
+      </c>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="16">
+        <v>3</v>
+      </c>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17">
+        <v>1</v>
+      </c>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17">
+        <v>1</v>
+      </c>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="16">
+        <v>4</v>
+      </c>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17">
+        <v>1</v>
+      </c>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17">
+        <v>1</v>
+      </c>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="16">
+        <v>5</v>
+      </c>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17">
+        <v>1</v>
+      </c>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17">
+        <v>1</v>
+      </c>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="16">
+        <v>6</v>
+      </c>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17">
+        <v>1</v>
+      </c>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17">
+        <v>1</v>
+      </c>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="16">
+        <v>7</v>
+      </c>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17">
+        <v>1</v>
+      </c>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17">
+        <v>1</v>
+      </c>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="16">
+        <v>8</v>
+      </c>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17">
+        <v>1</v>
+      </c>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17">
+        <v>1</v>
+      </c>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="16">
+        <v>9</v>
+      </c>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17">
+        <v>1</v>
+      </c>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17">
+        <v>1</v>
+      </c>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="16">
+        <v>10</v>
+      </c>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17">
+        <v>1</v>
+      </c>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17">
+        <v>1</v>
+      </c>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="16">
+        <v>11</v>
+      </c>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17">
+        <v>1</v>
+      </c>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17">
+        <v>1</v>
+      </c>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="16">
         <v>12</v>
       </c>
-      <c r="B27" s="10">
-        <f>_xlfn.STDEV.S(B6:B25)</f>
-        <v>0</v>
-      </c>
-      <c r="C27" s="15">
-        <f t="shared" ref="C27:G27" si="1">_xlfn.STDEV.S(C6:C25)</f>
-        <v>0.4893604849295935</v>
-      </c>
-      <c r="D27" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E27" s="15">
-        <f t="shared" si="1"/>
-        <v>0.44721359549995798</v>
-      </c>
-      <c r="F27" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="15">
-        <f t="shared" si="1"/>
-        <v>0.91046546800032602</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" s="11" t="s">
+      <c r="B39" s="17"/>
+      <c r="C39" s="17">
+        <v>2</v>
+      </c>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17">
+        <v>1</v>
+      </c>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="16">
+        <v>13</v>
+      </c>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17">
+        <v>1</v>
+      </c>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17">
+        <v>1</v>
+      </c>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="16">
+        <v>14</v>
+      </c>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17">
+        <v>1</v>
+      </c>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17">
+        <v>1</v>
+      </c>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="16">
+        <v>15</v>
+      </c>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17">
+        <v>1</v>
+      </c>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17">
+        <v>1</v>
+      </c>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="16">
+        <v>16</v>
+      </c>
+      <c r="B43" s="17"/>
+      <c r="C43" s="17">
+        <v>1</v>
+      </c>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17">
+        <v>1</v>
+      </c>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="16">
+        <v>17</v>
+      </c>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17">
+        <v>1</v>
+      </c>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17">
+        <v>1</v>
+      </c>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="16">
+        <v>18</v>
+      </c>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17">
+        <v>1</v>
+      </c>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17">
+        <v>1</v>
+      </c>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="16">
+        <v>19</v>
+      </c>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17">
+        <v>1</v>
+      </c>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17">
+        <v>1</v>
+      </c>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="16">
+        <v>20</v>
+      </c>
+      <c r="B47" s="17"/>
+      <c r="C47" s="17">
+        <v>1</v>
+      </c>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17">
+        <v>1</v>
+      </c>
+      <c r="F47" s="17"/>
+      <c r="G47" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10">
+        <f>SUM(C28:C47)/COUNT(C28:C47)</f>
+        <v>1.05</v>
+      </c>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10">
+        <f>SUM(E28:E47)/COUNT(E28:E47)</f>
+        <v>1</v>
+      </c>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10">
+        <f>SUM(G28:G47)/COUNT(G28:G47)</f>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="18">
-        <v>1</v>
-      </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19">
-        <v>1</v>
-      </c>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19">
-        <v>1</v>
-      </c>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="18">
-        <v>2</v>
-      </c>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19">
-        <v>1</v>
-      </c>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19">
-        <v>1</v>
-      </c>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="18">
-        <v>3</v>
-      </c>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19">
-        <v>1</v>
-      </c>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19">
-        <v>1</v>
-      </c>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="18">
-        <v>4</v>
-      </c>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19">
-        <v>1</v>
-      </c>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19">
-        <v>1</v>
-      </c>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="18">
-        <v>5</v>
-      </c>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19">
-        <v>1</v>
-      </c>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19">
-        <v>1</v>
-      </c>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="18">
-        <v>6</v>
-      </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19">
-        <v>1</v>
-      </c>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19">
-        <v>1</v>
-      </c>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="18">
-        <v>7</v>
-      </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19">
-        <v>1</v>
-      </c>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19">
-        <v>1</v>
-      </c>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="18">
-        <v>8</v>
-      </c>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19">
-        <v>1</v>
-      </c>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19">
-        <v>1</v>
-      </c>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="18">
-        <v>9</v>
-      </c>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19">
-        <v>1</v>
-      </c>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19">
-        <v>1</v>
-      </c>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="18">
-        <v>10</v>
-      </c>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19">
-        <v>1</v>
-      </c>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19">
-        <v>1</v>
-      </c>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="18">
-        <v>11</v>
-      </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19">
-        <v>1</v>
-      </c>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19">
-        <v>1</v>
-      </c>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="18">
-        <v>12</v>
-      </c>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19">
-        <v>2</v>
-      </c>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19">
-        <v>1</v>
-      </c>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="18">
-        <v>13</v>
-      </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19">
-        <v>1</v>
-      </c>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19">
-        <v>1</v>
-      </c>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="18">
-        <v>14</v>
-      </c>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19">
-        <v>1</v>
-      </c>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19">
-        <v>1</v>
-      </c>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="18">
-        <v>15</v>
-      </c>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19">
-        <v>1</v>
-      </c>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19">
-        <v>1</v>
-      </c>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="18">
-        <v>16</v>
-      </c>
-      <c r="B45" s="19"/>
-      <c r="C45" s="19">
-        <v>1</v>
-      </c>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19">
-        <v>1</v>
-      </c>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="18">
-        <v>17</v>
-      </c>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19">
-        <v>1</v>
-      </c>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19">
-        <v>1</v>
-      </c>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="18">
-        <v>18</v>
-      </c>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19">
-        <v>1</v>
-      </c>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19">
-        <v>1</v>
-      </c>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="18">
-        <v>19</v>
-      </c>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19">
-        <v>1</v>
-      </c>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19">
-        <v>1</v>
-      </c>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="18">
-        <v>20</v>
-      </c>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19">
-        <v>1</v>
-      </c>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19">
-        <v>1</v>
-      </c>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B50" s="10"/>
-      <c r="C50" s="10">
-        <f>SUM(C30:C49)/COUNT(C30:C49)</f>
-        <v>1.05</v>
-      </c>
-      <c r="D50" s="10"/>
-      <c r="E50" s="10">
-        <f>SUM(E30:E49)/COUNT(E30:E49)</f>
-        <v>1</v>
-      </c>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10">
-        <f>SUM(G30:G49)/COUNT(G30:G49)</f>
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10">
-        <f>_xlfn.STDEV.S(C30:C49)</f>
+      <c r="B49" s="10"/>
+      <c r="C49" s="10">
+        <f>_xlfn.STDEV.S(C28:C47)</f>
         <v>0.22360679774997888</v>
       </c>
-      <c r="D51" s="10"/>
-      <c r="E51" s="15">
-        <f>_xlfn.STDEV.S(E30:E49)</f>
-        <v>0</v>
-      </c>
-      <c r="F51" s="10"/>
-      <c r="G51" s="15">
-        <f>_xlfn.STDEV.S(G30:G49)</f>
+      <c r="D49" s="10"/>
+      <c r="E49" s="13">
+        <f>_xlfn.STDEV.S(E28:E47)</f>
+        <v>0</v>
+      </c>
+      <c r="F49" s="10"/>
+      <c r="G49" s="13">
+        <f>_xlfn.STDEV.S(G28:G47)</f>
         <v>0.3077935056255463</v>
       </c>
     </row>
@@ -4514,305 +4618,309 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EECEED4-571E-48A5-9D77-DAE9FDC1C5A1}">
   <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="19">
+        <v>1</v>
+      </c>
+      <c r="B4" s="19">
+        <v>5</v>
+      </c>
+      <c r="C4" s="19">
+        <v>1</v>
+      </c>
+      <c r="D4" s="19">
+        <v>3</v>
+      </c>
+      <c r="E4" s="19"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="19">
+        <v>2</v>
+      </c>
+      <c r="B5" s="19">
+        <v>5</v>
+      </c>
+      <c r="C5" s="19">
+        <v>0</v>
+      </c>
+      <c r="D5" s="19">
+        <v>5</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="19">
+        <v>3</v>
+      </c>
+      <c r="B6" s="19">
+        <v>5</v>
+      </c>
+      <c r="C6" s="19">
+        <v>1</v>
+      </c>
+      <c r="D6" s="19">
+        <v>4</v>
+      </c>
+      <c r="E6" s="19"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="19">
+        <v>4</v>
+      </c>
+      <c r="B7" s="19">
+        <v>5</v>
+      </c>
+      <c r="C7" s="19">
+        <v>1</v>
+      </c>
+      <c r="D7" s="19">
+        <v>3</v>
+      </c>
+      <c r="E7" s="19"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="19">
+        <v>5</v>
+      </c>
+      <c r="B8" s="19">
+        <v>5</v>
+      </c>
+      <c r="C8" s="19">
+        <v>0</v>
+      </c>
+      <c r="D8" s="19">
+        <v>5</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="19">
+        <v>6</v>
+      </c>
+      <c r="B9" s="19">
+        <v>3</v>
+      </c>
+      <c r="C9" s="19">
+        <v>0</v>
+      </c>
+      <c r="D9" s="19">
+        <v>5</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="19">
+        <v>7</v>
+      </c>
+      <c r="B10" s="19">
+        <v>3</v>
+      </c>
+      <c r="C10" s="19">
+        <v>1</v>
+      </c>
+      <c r="D10" s="19">
+        <v>2</v>
+      </c>
+      <c r="E10" s="19"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="19">
+        <v>8</v>
+      </c>
+      <c r="B11" s="19">
+        <v>3</v>
+      </c>
+      <c r="C11" s="19">
+        <v>1</v>
+      </c>
+      <c r="D11" s="19">
+        <v>4</v>
+      </c>
+      <c r="E11" s="19"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="19">
         <v>9</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="21">
-        <v>1</v>
-      </c>
-      <c r="B4" s="21">
+      <c r="B12" s="19">
+        <v>3</v>
+      </c>
+      <c r="C12" s="19">
+        <v>0</v>
+      </c>
+      <c r="D12" s="19">
         <v>5</v>
       </c>
-      <c r="C4" s="21">
-        <v>1</v>
-      </c>
-      <c r="D4" s="21">
+      <c r="E12" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="19">
+        <v>10</v>
+      </c>
+      <c r="B13" s="19">
         <v>3</v>
       </c>
-      <c r="E4" s="21"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="21">
+      <c r="C13" s="19">
+        <v>1</v>
+      </c>
+      <c r="D13" s="19">
+        <v>3</v>
+      </c>
+      <c r="E13" s="19"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="19">
+        <v>11</v>
+      </c>
+      <c r="B14" s="19">
         <v>2</v>
       </c>
-      <c r="B5" s="21">
+      <c r="C14" s="19">
+        <v>0</v>
+      </c>
+      <c r="D14" s="19">
         <v>5</v>
       </c>
-      <c r="C5" s="21">
-        <v>0</v>
-      </c>
-      <c r="D5" s="21">
+      <c r="E14" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="19">
+        <v>12</v>
+      </c>
+      <c r="B15" s="19">
+        <v>2</v>
+      </c>
+      <c r="C15" s="19">
+        <v>0</v>
+      </c>
+      <c r="D15" s="19">
         <v>5</v>
       </c>
-      <c r="E5" s="21" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="21">
+      <c r="E15" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="19">
+        <v>13</v>
+      </c>
+      <c r="B16" s="19">
+        <v>2</v>
+      </c>
+      <c r="C16" s="19">
+        <v>1</v>
+      </c>
+      <c r="D16" s="19">
+        <v>2</v>
+      </c>
+      <c r="E16" s="19"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="19">
+        <v>14</v>
+      </c>
+      <c r="B17" s="19">
+        <v>4</v>
+      </c>
+      <c r="C17" s="19">
+        <v>1</v>
+      </c>
+      <c r="D17" s="19">
         <v>3</v>
       </c>
-      <c r="B6" s="21">
+      <c r="E17" s="19"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="19">
+        <v>15</v>
+      </c>
+      <c r="B18" s="19">
+        <v>4</v>
+      </c>
+      <c r="C18" s="19">
+        <v>0</v>
+      </c>
+      <c r="D18" s="19">
         <v>5</v>
       </c>
-      <c r="C6" s="21">
-        <v>1</v>
-      </c>
-      <c r="D6" s="21">
+      <c r="E18" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="19">
+        <v>16</v>
+      </c>
+      <c r="B19" s="19">
         <v>4</v>
       </c>
-      <c r="E6" s="21"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="21">
+      <c r="C19" s="19">
+        <v>0</v>
+      </c>
+      <c r="D19" s="19">
+        <v>5</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="19">
+        <v>17</v>
+      </c>
+      <c r="B20" s="19">
         <v>4</v>
       </c>
-      <c r="B7" s="21">
+      <c r="C20" s="19">
+        <v>0</v>
+      </c>
+      <c r="D20" s="19">
         <v>5</v>
       </c>
-      <c r="C7" s="21">
-        <v>1</v>
-      </c>
-      <c r="D7" s="21">
-        <v>3</v>
-      </c>
-      <c r="E7" s="21"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="21">
-        <v>5</v>
-      </c>
-      <c r="B8" s="21">
-        <v>5</v>
-      </c>
-      <c r="C8" s="21">
-        <v>0</v>
-      </c>
-      <c r="D8" s="21">
-        <v>5</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="21">
-        <v>6</v>
-      </c>
-      <c r="B9" s="21">
-        <v>3</v>
-      </c>
-      <c r="C9" s="21">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21">
-        <v>5</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="21">
-        <v>7</v>
-      </c>
-      <c r="B10" s="21">
-        <v>3</v>
-      </c>
-      <c r="C10" s="21">
-        <v>1</v>
-      </c>
-      <c r="D10" s="21">
-        <v>2</v>
-      </c>
-      <c r="E10" s="21"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="21">
-        <v>8</v>
-      </c>
-      <c r="B11" s="21">
-        <v>3</v>
-      </c>
-      <c r="C11" s="21">
-        <v>1</v>
-      </c>
-      <c r="D11" s="21">
-        <v>4</v>
-      </c>
-      <c r="E11" s="21"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="21">
-        <v>9</v>
-      </c>
-      <c r="B12" s="21">
-        <v>3</v>
-      </c>
-      <c r="C12" s="21">
-        <v>0</v>
-      </c>
-      <c r="D12" s="21">
-        <v>5</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="21">
-        <v>10</v>
-      </c>
-      <c r="B13" s="21">
-        <v>3</v>
-      </c>
-      <c r="C13" s="21">
-        <v>1</v>
-      </c>
-      <c r="D13" s="21">
-        <v>3</v>
-      </c>
-      <c r="E13" s="21"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="21">
-        <v>11</v>
-      </c>
-      <c r="B14" s="21">
-        <v>2</v>
-      </c>
-      <c r="C14" s="21">
-        <v>0</v>
-      </c>
-      <c r="D14" s="21">
-        <v>5</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="21">
-        <v>12</v>
-      </c>
-      <c r="B15" s="21">
-        <v>2</v>
-      </c>
-      <c r="C15" s="21">
-        <v>0</v>
-      </c>
-      <c r="D15" s="21">
-        <v>5</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="21">
-        <v>13</v>
-      </c>
-      <c r="B16" s="21">
-        <v>2</v>
-      </c>
-      <c r="C16" s="21">
-        <v>1</v>
-      </c>
-      <c r="D16" s="21">
-        <v>2</v>
-      </c>
-      <c r="E16" s="21"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="21">
-        <v>14</v>
-      </c>
-      <c r="B17" s="21">
-        <v>4</v>
-      </c>
-      <c r="C17" s="21">
-        <v>1</v>
-      </c>
-      <c r="D17" s="21">
-        <v>3</v>
-      </c>
-      <c r="E17" s="21"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="21">
-        <v>15</v>
-      </c>
-      <c r="B18" s="21">
-        <v>4</v>
-      </c>
-      <c r="C18" s="21">
-        <v>0</v>
-      </c>
-      <c r="D18" s="21">
-        <v>5</v>
-      </c>
-      <c r="E18" s="21" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="21">
-        <v>16</v>
-      </c>
-      <c r="B19" s="21">
-        <v>4</v>
-      </c>
-      <c r="C19" s="21">
-        <v>0</v>
-      </c>
-      <c r="D19" s="21">
-        <v>5</v>
-      </c>
-      <c r="E19" s="21" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="21">
-        <v>17</v>
-      </c>
-      <c r="B20" s="21">
-        <v>4</v>
-      </c>
-      <c r="C20" s="21">
-        <v>0</v>
-      </c>
-      <c r="D20" s="21">
-        <v>5</v>
-      </c>
-      <c r="E20" s="21" t="s">
-        <v>65</v>
+      <c r="E20" s="19" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="3">
@@ -4840,7 +4948,7 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4852,20 +4960,20 @@
       <c r="Q1" s="1"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="20" t="s">
+      <c r="A2" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" s="18" t="s">
         <v>14</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>12</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -4882,600 +4990,600 @@
       <c r="T2" s="1"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="21">
-        <v>1</v>
-      </c>
-      <c r="B3" s="21">
-        <v>1</v>
-      </c>
-      <c r="C3" s="21">
+      <c r="A3" s="19">
+        <v>1</v>
+      </c>
+      <c r="B3" s="19">
+        <v>1</v>
+      </c>
+      <c r="C3" s="19">
         <v>2600</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="20">
         <f>C3*9.81/1000</f>
         <v>25.506</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="19">
         <v>1</v>
       </c>
       <c r="K3" s="2"/>
       <c r="R3" s="2"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="21">
+      <c r="A4" s="19">
         <v>2</v>
       </c>
-      <c r="B4" s="21">
-        <v>1</v>
-      </c>
-      <c r="C4" s="21">
+      <c r="B4" s="19">
+        <v>1</v>
+      </c>
+      <c r="C4" s="19">
         <v>2680</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="20">
         <f t="shared" ref="D4:D32" si="0">C4*9.81/1000</f>
         <v>26.290800000000004</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="19">
         <v>1</v>
       </c>
       <c r="K4" s="2"/>
       <c r="R4" s="2"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="21">
+      <c r="A5" s="19">
         <v>3</v>
       </c>
-      <c r="B5" s="21">
-        <v>1</v>
-      </c>
-      <c r="C5" s="21">
+      <c r="B5" s="19">
+        <v>1</v>
+      </c>
+      <c r="C5" s="19">
         <v>2500</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="20">
         <f t="shared" si="0"/>
         <v>24.524999999999999</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="19">
         <v>1</v>
       </c>
       <c r="K5" s="2"/>
       <c r="R5" s="2"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6" s="21">
+      <c r="A6" s="19">
         <v>4</v>
       </c>
-      <c r="B6" s="21">
-        <v>1</v>
-      </c>
-      <c r="C6" s="21">
+      <c r="B6" s="19">
+        <v>1</v>
+      </c>
+      <c r="C6" s="19">
         <v>2550</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="20">
         <f t="shared" si="0"/>
         <v>25.015499999999999</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="19">
         <v>1</v>
       </c>
       <c r="K6" s="2"/>
       <c r="R6" s="2"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" s="21">
+      <c r="A7" s="19">
         <v>5</v>
       </c>
-      <c r="B7" s="21">
-        <v>1</v>
-      </c>
-      <c r="C7" s="21">
+      <c r="B7" s="19">
+        <v>1</v>
+      </c>
+      <c r="C7" s="19">
         <v>2400</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="20">
         <f t="shared" si="0"/>
         <v>23.544</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="19">
         <v>1</v>
       </c>
       <c r="K7" s="2"/>
       <c r="R7" s="2"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" s="21">
+      <c r="A8" s="19">
         <v>6</v>
       </c>
-      <c r="B8" s="21">
-        <v>1</v>
-      </c>
-      <c r="C8" s="21">
+      <c r="B8" s="19">
+        <v>1</v>
+      </c>
+      <c r="C8" s="19">
         <v>2650</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="20">
         <f t="shared" si="0"/>
         <v>25.996500000000001</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="19">
         <v>1</v>
       </c>
       <c r="K8" s="2"/>
       <c r="R8" s="2"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" s="21">
+      <c r="A9" s="19">
         <v>7</v>
       </c>
-      <c r="B9" s="21">
-        <v>1</v>
-      </c>
-      <c r="C9" s="21">
+      <c r="B9" s="19">
+        <v>1</v>
+      </c>
+      <c r="C9" s="19">
         <v>2900</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="20">
         <f t="shared" si="0"/>
         <v>28.449000000000002</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="19">
         <v>1</v>
       </c>
       <c r="K9" s="2"/>
       <c r="R9" s="2"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" s="21">
+      <c r="A10" s="19">
         <v>8</v>
       </c>
-      <c r="B10" s="21">
-        <v>1</v>
-      </c>
-      <c r="C10" s="21">
+      <c r="B10" s="19">
+        <v>1</v>
+      </c>
+      <c r="C10" s="19">
         <v>2630</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="20">
         <f t="shared" si="0"/>
         <v>25.800300000000004</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="19">
         <v>1</v>
       </c>
       <c r="K10" s="2"/>
       <c r="R10" s="2"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A11" s="21">
+      <c r="A11" s="19">
         <v>9</v>
       </c>
-      <c r="B11" s="21">
-        <v>1</v>
-      </c>
-      <c r="C11" s="21">
+      <c r="B11" s="19">
+        <v>1</v>
+      </c>
+      <c r="C11" s="19">
         <v>2800</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="20">
         <f t="shared" si="0"/>
         <v>27.468</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="19">
         <v>1</v>
       </c>
       <c r="K11" s="2"/>
       <c r="R11" s="2"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A12" s="21">
+      <c r="A12" s="19">
         <v>10</v>
       </c>
-      <c r="B12" s="21">
-        <v>1</v>
-      </c>
-      <c r="C12" s="21">
+      <c r="B12" s="19">
+        <v>1</v>
+      </c>
+      <c r="C12" s="19">
         <v>2630</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="20">
         <f t="shared" si="0"/>
         <v>25.800300000000004</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="19">
         <v>1</v>
       </c>
       <c r="K12" s="2"/>
       <c r="R12" s="2"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A13" s="21">
+      <c r="A13" s="19">
         <v>11</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="19">
         <v>2</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="19">
         <v>4300</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="20">
         <f t="shared" si="0"/>
         <v>42.183</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="19">
         <v>1</v>
       </c>
       <c r="K13" s="2"/>
       <c r="R13" s="2"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A14" s="21">
+      <c r="A14" s="19">
         <v>12</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="19">
         <v>2</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="19">
         <v>4400</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="20">
         <f t="shared" si="0"/>
         <v>43.164000000000001</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="19">
         <v>1</v>
       </c>
       <c r="K14" s="2"/>
       <c r="R14" s="2"/>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A15" s="21">
+      <c r="A15" s="19">
         <v>13</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="19">
         <v>2</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="19">
         <v>3600</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="20">
         <f t="shared" si="0"/>
         <v>35.316000000000003</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="19">
         <v>1</v>
       </c>
       <c r="K15" s="2"/>
       <c r="R15" s="2"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A16" s="21">
+      <c r="A16" s="19">
         <v>14</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="19">
         <v>2</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="19">
         <v>3990</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="20">
         <f t="shared" si="0"/>
         <v>39.1419</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="19">
         <v>1</v>
       </c>
       <c r="K16" s="2"/>
       <c r="R16" s="2"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A17" s="21">
+      <c r="A17" s="19">
         <v>15</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="19">
         <v>2</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="19">
         <v>4200</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="20">
         <f t="shared" si="0"/>
         <v>41.201999999999998</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="19">
         <v>1</v>
       </c>
       <c r="K17" s="2"/>
       <c r="R17" s="2"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A18" s="21">
+      <c r="A18" s="19">
         <v>16</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="19">
         <v>2</v>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="19">
         <v>4600</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="20">
         <f t="shared" si="0"/>
         <v>45.125999999999998</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="19">
         <v>1</v>
       </c>
       <c r="K18" s="2"/>
       <c r="R18" s="2"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A19" s="21">
+      <c r="A19" s="19">
         <v>17</v>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="19">
         <v>2</v>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="19">
         <v>4530</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="20">
         <f t="shared" si="0"/>
         <v>44.439300000000003</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="19">
         <v>1</v>
       </c>
       <c r="K19" s="2"/>
       <c r="R19" s="2"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" s="21">
+      <c r="A20" s="19">
         <v>18</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="19">
         <v>2</v>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="19">
         <v>4450</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="20">
         <f t="shared" si="0"/>
         <v>43.654499999999999</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="19">
         <v>1</v>
       </c>
       <c r="K20" s="2"/>
       <c r="R20" s="2"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A21" s="21">
+      <c r="A21" s="19">
         <v>19</v>
       </c>
-      <c r="B21" s="21">
+      <c r="B21" s="19">
         <v>2</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="19">
         <v>4300</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="20">
         <f t="shared" si="0"/>
         <v>42.183</v>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="19">
         <v>1</v>
       </c>
       <c r="K21" s="2"/>
       <c r="R21" s="2"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" s="21">
+      <c r="A22" s="19">
         <v>20</v>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="19">
         <v>2</v>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="19">
         <v>4200</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="20">
         <f t="shared" si="0"/>
         <v>41.201999999999998</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="19">
         <v>1</v>
       </c>
       <c r="K22" s="2"/>
       <c r="R22" s="2"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A23" s="21">
+      <c r="A23" s="19">
         <v>21</v>
       </c>
-      <c r="B23" s="21">
+      <c r="B23" s="19">
         <v>3</v>
       </c>
-      <c r="C23" s="21">
+      <c r="C23" s="19">
         <v>4930</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="20">
         <f t="shared" si="0"/>
         <v>48.363300000000002</v>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="19">
         <v>1</v>
       </c>
       <c r="K23" s="2"/>
       <c r="R23" s="2"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A24" s="21">
+      <c r="A24" s="19">
         <v>22</v>
       </c>
-      <c r="B24" s="21">
+      <c r="B24" s="19">
         <v>3</v>
       </c>
-      <c r="C24" s="21">
+      <c r="C24" s="19">
         <v>4980</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="20">
         <f t="shared" si="0"/>
         <v>48.8538</v>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="19">
         <v>1</v>
       </c>
       <c r="K24" s="2"/>
       <c r="R24" s="2"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A25" s="21">
+      <c r="A25" s="19">
         <v>23</v>
       </c>
-      <c r="B25" s="21">
+      <c r="B25" s="19">
         <v>3</v>
       </c>
-      <c r="C25" s="21">
+      <c r="C25" s="19">
         <v>4270</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="20">
         <f t="shared" si="0"/>
         <v>41.888700000000007</v>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="19">
         <v>1</v>
       </c>
       <c r="K25" s="2"/>
       <c r="R25" s="2"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A26" s="21">
+      <c r="A26" s="19">
         <v>24</v>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="19">
         <v>3</v>
       </c>
-      <c r="C26" s="21">
+      <c r="C26" s="19">
         <v>4960</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="20">
         <f t="shared" si="0"/>
         <v>48.657600000000009</v>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="19">
         <v>1</v>
       </c>
       <c r="K26" s="2"/>
       <c r="R26" s="2"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A27" s="21">
+      <c r="A27" s="19">
         <v>25</v>
       </c>
-      <c r="B27" s="21">
+      <c r="B27" s="19">
         <v>3</v>
       </c>
-      <c r="C27" s="21">
+      <c r="C27" s="19">
         <v>4650</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="20">
         <f t="shared" si="0"/>
         <v>45.616500000000002</v>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="19">
         <v>1</v>
       </c>
       <c r="K27" s="2"/>
       <c r="R27" s="2"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A28" s="21">
+      <c r="A28" s="19">
         <v>26</v>
       </c>
-      <c r="B28" s="21">
+      <c r="B28" s="19">
         <v>3</v>
       </c>
-      <c r="C28" s="21">
+      <c r="C28" s="19">
         <v>4900</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="20">
         <f t="shared" si="0"/>
         <v>48.069000000000003</v>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="19">
         <v>1</v>
       </c>
       <c r="K28" s="2"/>
       <c r="R28" s="2"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A29" s="21">
+      <c r="A29" s="19">
         <v>27</v>
       </c>
-      <c r="B29" s="21">
+      <c r="B29" s="19">
         <v>3</v>
       </c>
-      <c r="C29" s="21">
+      <c r="C29" s="19">
         <v>4720</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="20">
         <f t="shared" si="0"/>
         <v>46.303200000000004</v>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="19">
         <v>1</v>
       </c>
       <c r="K29" s="2"/>
       <c r="R29" s="2"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A30" s="21">
+      <c r="A30" s="19">
         <v>28</v>
       </c>
-      <c r="B30" s="21">
+      <c r="B30" s="19">
         <v>3</v>
       </c>
-      <c r="C30" s="21">
+      <c r="C30" s="19">
         <v>4660</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="20">
         <f t="shared" si="0"/>
         <v>45.714600000000004</v>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="19">
         <v>1</v>
       </c>
       <c r="K30" s="2"/>
       <c r="R30" s="2"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A31" s="21">
+      <c r="A31" s="19">
         <v>29</v>
       </c>
-      <c r="B31" s="21">
+      <c r="B31" s="19">
         <v>3</v>
       </c>
-      <c r="C31" s="21">
+      <c r="C31" s="19">
         <v>4990</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="20">
         <f t="shared" si="0"/>
         <v>48.951900000000002</v>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="19">
         <v>1</v>
       </c>
       <c r="K31" s="2"/>
       <c r="R31" s="2"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A32" s="21">
+      <c r="A32" s="19">
         <v>30</v>
       </c>
-      <c r="B32" s="21">
+      <c r="B32" s="19">
         <v>3</v>
       </c>
-      <c r="C32" s="21">
+      <c r="C32" s="19">
         <v>4800</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="20">
         <f t="shared" si="0"/>
         <v>47.088000000000001</v>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="19">
         <v>1</v>
       </c>
       <c r="K32" s="2"/>
@@ -5513,27 +5621,27 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="D46" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -6149,200 +6257,200 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="19">
+        <v>1</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="19">
+        <v>1</v>
+      </c>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="19">
+        <v>2</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="19">
+        <v>1</v>
+      </c>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="19">
+        <v>3</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="19">
+        <v>0</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="19">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="19">
+        <v>4</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="19">
+        <v>1</v>
+      </c>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="19">
+        <v>5</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="19">
+        <v>1</v>
+      </c>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="19">
+        <v>6</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="19">
+        <v>1</v>
+      </c>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="19">
+        <v>7</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="19">
+        <v>0</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="19">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="19">
+        <v>8</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="19">
+        <v>1</v>
+      </c>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="19">
         <v>9</v>
       </c>
-      <c r="B2" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="21">
-        <v>1</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="21">
-        <v>1</v>
-      </c>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21">
+      <c r="B11" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="19">
+        <v>1</v>
+      </c>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19">
         <v>3.75</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="21">
-        <v>2</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="21">
-        <v>1</v>
-      </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="21">
-        <v>3</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="21">
-        <v>0</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="21">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="21">
-        <v>4</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="21">
-        <v>1</v>
-      </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="21">
-        <v>5</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="21">
-        <v>1</v>
-      </c>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="21">
-        <v>6</v>
-      </c>
-      <c r="B8" s="24" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="19">
+        <v>10</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="19">
+        <v>0</v>
+      </c>
+      <c r="D12" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="21">
-        <v>1</v>
-      </c>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="21">
-        <v>7</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="21">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="21">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="21">
-        <v>8</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="21">
-        <v>1</v>
-      </c>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="21">
-        <v>9</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="21">
-        <v>1</v>
-      </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="21">
-        <v>10</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="21">
-        <v>0</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="21">
+      <c r="E12" s="19">
         <v>3.75</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -6366,620 +6474,620 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="23" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="25" t="s">
+      <c r="F2" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="25" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="22">
-        <v>1</v>
-      </c>
-      <c r="B3" s="22">
+      <c r="A3" s="20">
+        <v>1</v>
+      </c>
+      <c r="B3" s="20">
         <v>32.467400000000005</v>
       </c>
-      <c r="C3" s="22">
+      <c r="C3" s="20">
         <f t="shared" ref="C3:C16" si="0">B3-$B$37</f>
         <v>32.467400000000005</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="20">
         <v>0.46740000000000492</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="20">
         <v>10.329199999999998</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="20">
         <f t="shared" ref="F3:F16" si="1">E3-$E$37</f>
         <v>10.329199999999998</v>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="20">
         <v>1.6228799999999999</v>
       </c>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="22">
+      <c r="A4" s="20">
         <v>2</v>
       </c>
-      <c r="B4" s="22">
+      <c r="B4" s="20">
         <v>32.173400000000001</v>
       </c>
-      <c r="C4" s="22">
+      <c r="C4" s="20">
         <f t="shared" si="0"/>
         <v>32.173400000000001</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="20">
         <v>0.17340000000000089</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="20">
         <v>10.7212</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="20">
         <f t="shared" si="1"/>
         <v>10.7212</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="20">
         <v>1.3915999999999999</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="22">
+      <c r="A5" s="20">
         <v>3</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="20">
         <v>31.928399999999996</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="20">
         <f t="shared" si="0"/>
         <v>31.928399999999996</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="20">
         <v>-7.1600000000003661E-2</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="20">
         <v>10.6624</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="20">
         <f t="shared" si="1"/>
         <v>10.6624</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="20">
         <v>2.3029999999999999</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="22">
+      <c r="A6" s="20">
         <v>4</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="20">
         <v>32.045999999999999</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="20">
         <f t="shared" si="0"/>
         <v>32.045999999999999</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="20">
         <v>4.5999999999999375E-2</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="20">
         <v>10.29</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="20">
         <f t="shared" si="1"/>
         <v>10.29</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="20">
         <v>0.44982</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="22">
+      <c r="A7" s="20">
         <v>5</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="20">
         <v>32.202799999999996</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="20">
         <f t="shared" si="0"/>
         <v>32.202799999999996</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="20">
         <v>0.20279999999999632</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="20">
         <v>10.407599999999999</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="20">
         <f t="shared" si="1"/>
         <v>10.407599999999999</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="20">
         <v>1.6856</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="22">
+      <c r="A8" s="20">
         <v>6</v>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="20">
         <v>31.683399999999999</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="20">
         <f t="shared" si="0"/>
         <v>31.683399999999999</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="20">
         <v>-0.3166000000000011</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="20">
         <v>9.8391999999999982</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="20">
         <f t="shared" si="1"/>
         <v>9.8391999999999982</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="20">
         <v>1.1367999999999998</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="22">
+      <c r="A9" s="20">
         <v>7</v>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="20">
         <v>32.565399999999997</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="20">
         <f t="shared" si="0"/>
         <v>32.565399999999997</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="20">
         <v>0.56539999999999679</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="20">
         <v>10.5252</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="20">
         <f t="shared" si="1"/>
         <v>10.5252</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="20">
         <v>0.98980000000000001</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="22">
+      <c r="A10" s="20">
         <v>8</v>
       </c>
-      <c r="B10" s="22">
+      <c r="B10" s="20">
         <v>31.8108</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="20">
         <f t="shared" si="0"/>
         <v>31.8108</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="20">
         <v>-0.18919999999999959</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="20">
         <v>9.9372000000000007</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="20">
         <f t="shared" si="1"/>
         <v>9.9372000000000007</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="20">
         <v>0.92119999999999991</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="22">
+      <c r="A11" s="20">
         <v>9</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="20">
         <v>31.458000000000002</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="20">
         <f t="shared" si="0"/>
         <v>31.458000000000002</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="20">
         <v>-0.54199999999999804</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="20">
         <v>9.9862000000000002</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="20">
         <f t="shared" si="1"/>
         <v>9.9862000000000002</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="20">
         <v>0.40179999999999999</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="22">
+      <c r="A12" s="20">
         <v>10</v>
       </c>
-      <c r="B12" s="22">
+      <c r="B12" s="20">
         <v>31.840200000000003</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="20">
         <f t="shared" si="0"/>
         <v>31.840200000000003</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="20">
         <v>-0.15979999999999706</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="20">
         <v>10.211599999999999</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="20">
         <f t="shared" si="1"/>
         <v>10.211599999999999</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="20">
         <v>1.2054</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="22">
+      <c r="A13" s="20">
         <v>11</v>
       </c>
-      <c r="B13" s="22">
+      <c r="B13" s="20">
         <v>32.016600000000004</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="20">
         <f t="shared" si="0"/>
         <v>32.016600000000004</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="20">
         <v>1.6600000000003945E-2</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="20">
         <v>10.152799999999999</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="20">
         <f t="shared" si="1"/>
         <v>10.152799999999999</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="20">
         <v>0.80359999999999998</v>
       </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="22">
+      <c r="A14" s="20">
         <v>12</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="20">
         <v>32.2714</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="20">
         <f t="shared" si="0"/>
         <v>32.2714</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="20">
         <v>0.27139999999999986</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="20">
         <v>9.9959999999999987</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="20">
         <f t="shared" si="1"/>
         <v>9.9959999999999987</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="20">
         <v>1.1172</v>
       </c>
       <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="22">
+      <c r="A15" s="20">
         <v>13</v>
       </c>
-      <c r="B15" s="22">
+      <c r="B15" s="20">
         <v>32.065599999999996</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="20">
         <f t="shared" si="0"/>
         <v>32.065599999999996</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="20">
         <v>6.5599999999996328E-2</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="20">
         <v>10.368399999999999</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="20">
         <f t="shared" si="1"/>
         <v>10.368399999999999</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="20">
         <v>0.99960000000000004</v>
       </c>
       <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="22">
+      <c r="A16" s="20">
         <v>14</v>
       </c>
-      <c r="B16" s="22">
+      <c r="B16" s="20">
         <v>32.2714</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="20">
         <f t="shared" si="0"/>
         <v>32.2714</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="20">
         <v>0.27139999999999986</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="20">
         <v>10.0548</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="20">
         <f t="shared" si="1"/>
         <v>10.0548</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="20">
         <v>0.7056</v>
       </c>
       <c r="H16" s="2"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="25">
+      <c r="A17" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="23">
         <v>0.29007378371717746</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="23">
         <f t="shared" ref="C17" si="2">_xlfn.STDEV.P(C3:C16)</f>
         <v>0.29007378371717746</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="23">
         <v>0.2900737837171774</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="23">
         <v>0.26244399402539209</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="23">
         <f>_xlfn.STDEV.P(F3:F16)</f>
         <v>0.26244399402539209</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="23">
         <v>0.48998406474088496</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="25">
+      <c r="A18" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="23">
         <v>32.057200000000002</v>
       </c>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25">
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23">
         <v>10.248699999999999</v>
       </c>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25">
+      <c r="F18" s="23"/>
+      <c r="G18" s="23">
         <v>1.1238500000000002</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="B19" s="25">
+      <c r="A19" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="B19" s="23">
         <v>32</v>
       </c>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25">
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23">
         <v>10</v>
       </c>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
       <c r="H19" s="2"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="26"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
+      <c r="A21" s="24"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="27"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
+      <c r="A22" s="25"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="27"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
+      <c r="A23" s="25"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="27"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
+      <c r="A24" s="25"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="27"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
+      <c r="A25" s="25"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="27"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
+      <c r="A26" s="25"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="27"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
+      <c r="A27" s="25"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="27"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
+      <c r="A28" s="25"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="27"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
+      <c r="A29" s="25"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="27"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
+      <c r="A30" s="25"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="27"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
+      <c r="A31" s="25"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="27"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
+      <c r="A32" s="25"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="27"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
+      <c r="A33" s="25"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="27"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
+      <c r="A34" s="25"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="27"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
+      <c r="A35" s="25"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="26"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="26"/>
+      <c r="A36" s="24"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="26"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
+      <c r="A37" s="24"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="29"/>
-      <c r="B38" s="29"/>
-      <c r="C38" s="29"/>
-      <c r="D38" s="29"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
-      <c r="G38" s="29"/>
+      <c r="A38" s="27"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6998,299 +7106,299 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>64</v>
+      <c r="A2" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="21">
-        <v>1</v>
-      </c>
-      <c r="B3" s="21">
+      <c r="A3" s="19">
+        <v>1</v>
+      </c>
+      <c r="B3" s="19">
         <v>10</v>
       </c>
-      <c r="C3" s="21">
-        <v>0</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>106</v>
+      <c r="C3" s="19">
+        <v>0</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="21">
+      <c r="A4" s="19">
         <v>2</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="19">
         <v>15</v>
       </c>
-      <c r="C4" s="21">
-        <v>0</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>106</v>
+      <c r="C4" s="19">
+        <v>0</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="21">
+      <c r="A5" s="19">
         <v>3</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="19">
         <v>20</v>
       </c>
-      <c r="C5" s="21">
-        <v>0</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>106</v>
+      <c r="C5" s="19">
+        <v>0</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="21">
+      <c r="A6" s="19">
         <v>4</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="19">
         <v>25</v>
       </c>
-      <c r="C6" s="21">
-        <v>0</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>106</v>
+      <c r="C6" s="19">
+        <v>0</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="21">
+      <c r="A7" s="19">
         <v>5</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="19">
         <v>30</v>
       </c>
-      <c r="C7" s="21">
-        <v>0</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>106</v>
+      <c r="C7" s="19">
+        <v>0</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="21">
+      <c r="A8" s="19">
         <v>6</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="19">
         <v>35</v>
       </c>
-      <c r="C8" s="21">
-        <v>1</v>
-      </c>
-      <c r="D8" s="21"/>
+      <c r="C8" s="19">
+        <v>1</v>
+      </c>
+      <c r="D8" s="19"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="21">
+      <c r="A9" s="19">
         <v>7</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="19">
         <v>35</v>
       </c>
-      <c r="C9" s="21">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>106</v>
+      <c r="C9" s="19">
+        <v>0</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="21">
+      <c r="A10" s="19">
         <v>8</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="19">
         <v>35</v>
       </c>
-      <c r="C10" s="21">
-        <v>1</v>
-      </c>
-      <c r="D10" s="21"/>
+      <c r="C10" s="19">
+        <v>1</v>
+      </c>
+      <c r="D10" s="19"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="21">
+      <c r="A11" s="19">
         <v>9</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="19">
         <v>35</v>
       </c>
-      <c r="C11" s="21">
-        <v>0</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>106</v>
+      <c r="C11" s="19">
+        <v>0</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="21">
+      <c r="A12" s="19">
         <v>10</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="19">
         <v>37.5</v>
       </c>
-      <c r="C12" s="21">
-        <v>0</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>107</v>
+      <c r="C12" s="19">
+        <v>0</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="21">
+      <c r="A13" s="19">
         <v>11</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="19">
         <v>37.5</v>
       </c>
-      <c r="C13" s="21">
-        <v>1</v>
-      </c>
-      <c r="D13" s="21"/>
+      <c r="C13" s="19">
+        <v>1</v>
+      </c>
+      <c r="D13" s="19"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="21">
+      <c r="A14" s="19">
         <v>12</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="19">
         <v>37.5</v>
       </c>
-      <c r="C14" s="21">
-        <v>1</v>
-      </c>
-      <c r="D14" s="21"/>
+      <c r="C14" s="19">
+        <v>1</v>
+      </c>
+      <c r="D14" s="19"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="21">
+      <c r="A15" s="19">
         <v>13</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="19">
         <v>37.5</v>
       </c>
-      <c r="C15" s="21">
-        <v>1</v>
-      </c>
-      <c r="D15" s="21"/>
+      <c r="C15" s="19">
+        <v>1</v>
+      </c>
+      <c r="D15" s="19"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="21">
+      <c r="A16" s="19">
         <v>14</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="19">
         <v>40</v>
       </c>
-      <c r="C16" s="21">
-        <v>0</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>107</v>
+      <c r="C16" s="19">
+        <v>0</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="21">
+      <c r="A17" s="19">
         <v>15</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="19">
         <v>40</v>
       </c>
-      <c r="C17" s="21">
-        <v>1</v>
-      </c>
-      <c r="D17" s="21"/>
+      <c r="C17" s="19">
+        <v>1</v>
+      </c>
+      <c r="D17" s="19"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="21">
+      <c r="A18" s="19">
         <v>16</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="19">
         <v>40</v>
       </c>
-      <c r="C18" s="21">
-        <v>1</v>
-      </c>
-      <c r="D18" s="21"/>
+      <c r="C18" s="19">
+        <v>1</v>
+      </c>
+      <c r="D18" s="19"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="21">
+      <c r="A19" s="19">
         <v>17</v>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="19">
         <v>40</v>
       </c>
-      <c r="C19" s="21">
-        <v>0</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>107</v>
+      <c r="C19" s="19">
+        <v>0</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="21">
+      <c r="A20" s="19">
         <v>18</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="19">
         <v>42.5</v>
       </c>
-      <c r="C20" s="21">
-        <v>0</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>107</v>
+      <c r="C20" s="19">
+        <v>0</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="21">
+      <c r="A21" s="19">
         <v>19</v>
       </c>
-      <c r="B21" s="21">
+      <c r="B21" s="19">
         <v>42.5</v>
       </c>
-      <c r="C21" s="21">
-        <v>1</v>
-      </c>
-      <c r="D21" s="21"/>
+      <c r="C21" s="19">
+        <v>1</v>
+      </c>
+      <c r="D21" s="19"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="21">
+      <c r="A22" s="19">
         <v>20</v>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="19">
         <v>42.5</v>
       </c>
-      <c r="C22" s="21">
-        <v>0</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>107</v>
+      <c r="C22" s="19">
+        <v>0</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="21">
+      <c r="A23" s="19">
         <v>21</v>
       </c>
-      <c r="B23" s="21">
+      <c r="B23" s="19">
         <v>42.5</v>
       </c>
-      <c r="C23" s="21">
-        <v>0</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>107</v>
+      <c r="C23" s="19">
+        <v>0</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -7300,7 +7408,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4B1570B-4DCB-4D7F-9F26-A58A053E3FAA}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
@@ -7314,162 +7422,162 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="19">
+        <v>1</v>
+      </c>
+      <c r="B3" s="19">
+        <v>1</v>
+      </c>
+      <c r="C3" s="19">
+        <v>5</v>
+      </c>
+      <c r="D3" s="19">
+        <f>B3*$B$10+C3*$C$10+$D$10</f>
+        <v>10.4</v>
+      </c>
+      <c r="E3" s="28">
+        <f>D3*9.81</f>
+        <v>102.02400000000002</v>
+      </c>
+      <c r="F3" s="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="19">
+        <v>2</v>
+      </c>
+      <c r="B4" s="19">
+        <v>2</v>
+      </c>
+      <c r="C4" s="19">
+        <v>4</v>
+      </c>
+      <c r="D4" s="19">
+        <f>B4*$B$10+C4*$C$10+$D$10</f>
+        <v>9</v>
+      </c>
+      <c r="E4" s="28">
+        <f t="shared" ref="E4:E7" si="0">D4*9.81</f>
+        <v>88.29</v>
+      </c>
+      <c r="F4" s="19">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="19">
+        <v>3</v>
+      </c>
+      <c r="B5" s="19">
+        <v>0</v>
+      </c>
+      <c r="C5" s="19">
+        <v>5</v>
+      </c>
+      <c r="D5" s="19">
+        <f>B5*$B$10+C5*$C$10+$D$10</f>
+        <v>9.85</v>
+      </c>
+      <c r="E5" s="28">
+        <f t="shared" si="0"/>
+        <v>96.628500000000003</v>
+      </c>
+      <c r="F5" s="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="19">
+        <v>4</v>
+      </c>
+      <c r="B6" s="19">
+        <v>1</v>
+      </c>
+      <c r="C6" s="19">
+        <v>4</v>
+      </c>
+      <c r="D6" s="19">
+        <f>B6*$B$10+C6*$C$10+$D$10</f>
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="E6" s="28">
+        <f t="shared" si="0"/>
+        <v>82.894499999999994</v>
+      </c>
+      <c r="F6" s="19">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="19">
+        <v>5</v>
+      </c>
+      <c r="B7" s="19">
+        <v>1</v>
+      </c>
+      <c r="C7" s="19">
+        <v>5</v>
+      </c>
+      <c r="D7" s="19">
+        <f>B7*$B$10+C7*$C$10+$D$10</f>
+        <v>10.4</v>
+      </c>
+      <c r="E7" s="28">
+        <f t="shared" si="0"/>
+        <v>102.02400000000002</v>
+      </c>
+      <c r="F7" s="19">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="18" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="21">
-        <v>1</v>
-      </c>
-      <c r="B4" s="21">
-        <v>1</v>
-      </c>
-      <c r="C4" s="21">
-        <v>5</v>
-      </c>
-      <c r="D4" s="21">
-        <f>B4*$B$11+C4*$C$11+$D$11</f>
-        <v>10.4</v>
-      </c>
-      <c r="E4" s="30">
-        <f>D4*9.81</f>
-        <v>102.02400000000002</v>
-      </c>
-      <c r="F4" s="21">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="21">
-        <v>2</v>
-      </c>
-      <c r="B5" s="21">
-        <v>2</v>
-      </c>
-      <c r="C5" s="21">
-        <v>4</v>
-      </c>
-      <c r="D5" s="21">
-        <f t="shared" ref="D5:D8" si="0">B5*$B$11+C5*$C$11+$D$11</f>
-        <v>9</v>
-      </c>
-      <c r="E5" s="30">
-        <f t="shared" ref="E5:E8" si="1">D5*9.81</f>
-        <v>88.29</v>
-      </c>
-      <c r="F5" s="21">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="21">
-        <v>3</v>
-      </c>
-      <c r="B6" s="21">
-        <v>0</v>
-      </c>
-      <c r="C6" s="21">
-        <v>5</v>
-      </c>
-      <c r="D6" s="21">
-        <f t="shared" si="0"/>
-        <v>9.85</v>
-      </c>
-      <c r="E6" s="30">
-        <f t="shared" si="1"/>
-        <v>96.628500000000003</v>
-      </c>
-      <c r="F6" s="21">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="21">
-        <v>4</v>
-      </c>
-      <c r="B7" s="21">
-        <v>1</v>
-      </c>
-      <c r="C7" s="21">
-        <v>4</v>
-      </c>
-      <c r="D7" s="21">
-        <f t="shared" si="0"/>
-        <v>8.4499999999999993</v>
-      </c>
-      <c r="E7" s="30">
-        <f t="shared" si="1"/>
-        <v>82.894499999999994</v>
-      </c>
-      <c r="F7" s="21">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="21">
-        <v>5</v>
-      </c>
-      <c r="B8" s="21">
-        <v>1</v>
-      </c>
-      <c r="C8" s="21">
-        <v>5</v>
-      </c>
-      <c r="D8" s="21">
-        <f t="shared" si="0"/>
-        <v>10.4</v>
-      </c>
-      <c r="E8" s="30">
-        <f t="shared" si="1"/>
-        <v>102.02400000000002</v>
-      </c>
-      <c r="F8" s="21">
-        <v>4.5</v>
+      <c r="D9" s="18" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="21"/>
-      <c r="B11" s="21">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19">
         <v>0.55000000000000004</v>
       </c>
-      <c r="C11" s="21">
+      <c r="C10" s="19">
         <v>1.95</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D10" s="19">
         <v>0.1</v>
       </c>
     </row>

--- a/Test_data/Boolean and force tests/Master charts.xlsx
+++ b/Test_data/Boolean and force tests/Master charts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dokumenter\Skole\Master\Master-s-Thesis\Test_data\Boolean and force tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9594BC-FAE4-4C95-BE36-C5E14FECA0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{997542D0-CAC7-44BD-B260-25F468971CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" firstSheet="1" activeTab="1" xr2:uid="{183E3E47-5F56-400D-983A-CDA78A52BF4C}"/>
+    <workbookView xWindow="1848" yWindow="0" windowWidth="16956" windowHeight="9696" firstSheet="4" activeTab="5" xr2:uid="{183E3E47-5F56-400D-983A-CDA78A52BF4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" state="hidden" r:id="rId1"/>
@@ -618,7 +618,7 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -638,7 +638,7 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -649,16 +649,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="5" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="5" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="8" fillId="5" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Dårlig" xfId="4" builtinId="27"/>
@@ -3537,29 +3533,29 @@
       <c r="A13" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="29">
         <f>SUM(B3:B12)/COUNTA(B3:B12)*100</f>
         <v>100</v>
       </c>
-      <c r="C13" s="30"/>
+      <c r="C13" s="27"/>
       <c r="D13" s="18"/>
-      <c r="E13" s="32">
+      <c r="E13" s="29">
         <f t="shared" ref="E13" si="0">SUM(E3:E12)/COUNTA(E3:E12)*100</f>
         <v>100</v>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="29">
         <f t="shared" ref="F13" si="1">SUM(F3:F12)/COUNTA(F3:F12)*100</f>
         <v>100</v>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="29">
         <f t="shared" ref="G13" si="2">SUM(G3:G12)/COUNTA(G3:G12)*100</f>
         <v>100</v>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="27">
         <f t="shared" ref="H13" si="3">SUM(H3:H12)/COUNTA(H3:H12)*100</f>
         <v>70</v>
       </c>
-      <c r="I13" s="30">
+      <c r="I13" s="27">
         <f>(B13*E13*F13*G13*H13)/100^4</f>
         <v>70</v>
       </c>
@@ -3568,37 +3564,37 @@
       <c r="A16" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="26">
         <v>0.46666666666666667</v>
       </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="27">
         <f>I13/100</f>
         <v>0.7</v>
       </c>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="26">
         <f>B16*B17</f>
         <v>0.32666666666666666</v>
       </c>
       <c r="C18" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="28">
         <f>B18*100</f>
         <v>32.666666666666664</v>
       </c>
@@ -3607,12 +3603,12 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="33" t="s">
+      <c r="A20" s="1" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="33" t="s">
+      <c r="A21" s="1" t="s">
         <v>127</v>
       </c>
     </row>
@@ -6282,12 +6278,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C3" s="19">
-        <v>1</v>
-      </c>
-      <c r="D3" s="19"/>
+        <v>0</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>35</v>
+      </c>
       <c r="E3" s="19">
         <v>3.75</v>
       </c>
@@ -6297,7 +6295,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="19">
         <v>1</v>
@@ -6312,14 +6310,12 @@
         <v>3</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C5" s="19">
-        <v>0</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>35</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D5" s="19"/>
       <c r="E5" s="19">
         <v>3.75</v>
       </c>
@@ -6329,7 +6325,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C6" s="19">
         <v>1</v>
@@ -6344,7 +6340,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" s="19">
         <v>1</v>
@@ -6359,7 +6355,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" s="19">
         <v>1</v>
@@ -6377,11 +6373,9 @@
         <v>31</v>
       </c>
       <c r="C9" s="19">
-        <v>0</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>35</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D9" s="19"/>
       <c r="E9" s="19">
         <v>3.75</v>
       </c>
@@ -6391,12 +6385,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" s="19">
-        <v>1</v>
-      </c>
-      <c r="D10" s="19"/>
+        <v>0</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>35</v>
+      </c>
       <c r="E10" s="19">
         <v>3.75</v>
       </c>
@@ -6928,166 +6924,166 @@
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="24"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
+      <c r="A22" s="24"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="25"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
+      <c r="A23" s="24"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
+      <c r="A24" s="24"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
+      <c r="A25" s="24"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
+      <c r="A26" s="24"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="25"/>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
+      <c r="A27" s="24"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="25"/>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
+      <c r="A28" s="24"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="25"/>
-      <c r="B29" s="26"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
+      <c r="A29" s="24"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="25"/>
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
+      <c r="A30" s="24"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="25"/>
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
+      <c r="A31" s="24"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="25"/>
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
+      <c r="A32" s="24"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="25"/>
-      <c r="B33" s="26"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
+      <c r="A33" s="24"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="25"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
+      <c r="A34" s="24"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="25"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
+      <c r="A35" s="24"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="24"/>
-      <c r="B36" s="24"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="24"/>
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="24"/>
-      <c r="B37" s="24"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="27"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7459,7 +7455,7 @@
         <f>B3*$B$10+C3*$C$10+$D$10</f>
         <v>10.4</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="25">
         <f>D3*9.81</f>
         <v>102.02400000000002</v>
       </c>
@@ -7481,7 +7477,7 @@
         <f>B4*$B$10+C4*$C$10+$D$10</f>
         <v>9</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="25">
         <f t="shared" ref="E4:E7" si="0">D4*9.81</f>
         <v>88.29</v>
       </c>
@@ -7503,7 +7499,7 @@
         <f>B5*$B$10+C5*$C$10+$D$10</f>
         <v>9.85</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="25">
         <f t="shared" si="0"/>
         <v>96.628500000000003</v>
       </c>
@@ -7525,7 +7521,7 @@
         <f>B6*$B$10+C6*$C$10+$D$10</f>
         <v>8.4499999999999993</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="25">
         <f t="shared" si="0"/>
         <v>82.894499999999994</v>
       </c>
@@ -7547,7 +7543,7 @@
         <f>B7*$B$10+C7*$C$10+$D$10</f>
         <v>10.4</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="25">
         <f t="shared" si="0"/>
         <v>102.02400000000002</v>
       </c>
